--- a/Pruebas calificadas/COLEGIO FRANCISCO DE MIRANDA-703_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO FRANCISCO DE MIRANDA-703_CALIFICADO.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ63"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15716,6 +15716,352 @@
         <v/>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>111001014974</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>DANIEL FELIPE PEREZ PARRADO</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>1012922767</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>703</v>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr"/>
+      <c r="X64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE64" s="2" t="inlineStr"/>
+      <c r="AF64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG64" s="2" t="inlineStr"/>
+      <c r="AH64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI64" s="2" t="inlineStr"/>
+      <c r="AJ64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK64" s="2" t="inlineStr"/>
+      <c r="AL64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM64" s="2" t="inlineStr"/>
+      <c r="AN64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO64" s="2" t="inlineStr"/>
+      <c r="AP64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ64" s="2" t="inlineStr"/>
+      <c r="AR64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS64" s="2" t="inlineStr"/>
+      <c r="AT64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU64" s="2" t="inlineStr"/>
+      <c r="AV64" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW64" s="5">
+        <f>COUNTIF(J64:AV64,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX64" s="5">
+        <f>COUNTIF(J64:AV64,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY64" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ64" s="6">
+        <f>AW64/AY64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>111001014974</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>JUAN ESTEBAN VALLEJO ROMERO</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>1146129401</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>703</v>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr"/>
+      <c r="AB65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE65" s="2" t="inlineStr"/>
+      <c r="AF65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG65" s="2" t="inlineStr"/>
+      <c r="AH65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI65" s="2" t="inlineStr"/>
+      <c r="AJ65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK65" s="2" t="inlineStr"/>
+      <c r="AL65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM65" s="2" t="inlineStr"/>
+      <c r="AN65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO65" s="2" t="inlineStr"/>
+      <c r="AP65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ65" s="2" t="inlineStr"/>
+      <c r="AR65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS65" s="2" t="inlineStr"/>
+      <c r="AT65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU65" s="2" t="inlineStr"/>
+      <c r="AV65" s="4" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW65" s="5">
+        <f>COUNTIF(J65:AV65,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX65" s="5">
+        <f>COUNTIF(J65:AV65,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY65" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ65" s="6">
+        <f>AW65/AY65</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pruebas calificadas/COLEGIO FRANCISCO DE MIRANDA-703_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO FRANCISCO DE MIRANDA-703_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2064,11 +2044,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -2076,7 +2052,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2317,11 +2293,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -2329,7 +2301,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2570,11 +2542,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -2582,7 +2550,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2823,11 +2791,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -2835,7 +2799,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2996,11 +2960,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -3008,7 +2968,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3205,11 +3165,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -3217,7 +3173,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3382,11 +3338,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -3394,7 +3346,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3635,11 +3587,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -3647,7 +3595,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3888,11 +3836,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -3900,7 +3844,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4141,11 +4085,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -4153,7 +4093,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4394,11 +4334,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -4406,7 +4342,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4647,11 +4583,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -4659,7 +4591,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4896,11 +4828,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -4908,7 +4836,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5069,11 +4997,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -5081,7 +5005,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5322,11 +5246,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -5334,7 +5254,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5499,11 +5419,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -5511,7 +5427,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -5752,11 +5668,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -5764,7 +5676,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5925,11 +5837,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -5937,7 +5845,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6178,11 +6086,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -6190,7 +6094,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6431,11 +6335,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -6443,7 +6343,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -6680,11 +6580,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -6692,7 +6588,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6933,11 +6829,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -6945,7 +6837,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7186,11 +7078,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -7198,7 +7086,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7439,11 +7327,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -7451,7 +7335,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -7692,11 +7576,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -7704,7 +7584,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -7941,11 +7821,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -7953,7 +7829,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8194,11 +8070,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -8206,7 +8078,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8447,11 +8319,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -8459,7 +8327,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -8700,11 +8568,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -8712,7 +8576,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -8953,11 +8817,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -8965,7 +8825,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9142,11 +9002,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -9154,7 +9010,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9395,11 +9251,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -9407,7 +9259,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -9648,11 +9500,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -9660,7 +9508,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -9901,11 +9749,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -9913,7 +9757,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10154,11 +9998,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -10166,7 +10006,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10407,11 +10247,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -10419,7 +10255,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -10616,11 +10452,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -10628,7 +10460,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -10869,11 +10701,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -10881,7 +10709,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11122,11 +10950,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -11134,7 +10958,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11375,11 +11199,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -11387,7 +11207,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -11624,11 +11444,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -11636,7 +11452,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -11877,11 +11693,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -11889,7 +11701,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12130,11 +11942,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -12142,7 +11950,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12383,11 +12191,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -12395,7 +12199,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -12636,11 +12440,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -12648,7 +12448,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -12889,11 +12689,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -12901,7 +12697,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13062,11 +12858,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -13074,7 +12866,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13315,11 +13107,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -13327,7 +13115,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -13488,11 +13276,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -13500,7 +13284,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -13741,11 +13525,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -13753,7 +13533,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -13994,11 +13774,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -14006,7 +13782,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14247,11 +14023,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -14259,7 +14031,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -14500,11 +14272,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -14512,7 +14280,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -14753,11 +14521,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -14765,7 +14529,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15006,11 +14770,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -15018,7 +14778,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15259,11 +15019,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -15271,7 +15027,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -15464,11 +15220,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -15476,7 +15228,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -15717,11 +15469,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -15729,7 +15477,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -15890,11 +15638,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -15902,7 +15646,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
